--- a/samples/hakim/Future summer 2026.xlsx
+++ b/samples/hakim/Future summer 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mdlogistiquecom-my.sharepoint.com/personal/info_mdlogistique_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="121" documentId="14_{AB3E179F-3F7F-4316-B917-40370EE6D713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6FA1097-863D-D545-8690-4C68F80FA27E}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="14_{AB3E179F-3F7F-4316-B917-40370EE6D713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{480E0978-1D50-8240-9BA7-09073A9D1373}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="83">
   <si>
     <t>1ZX665X60492651977</t>
   </si>
@@ -165,6 +165,123 @@
   </si>
   <si>
     <t>1Z3X64X46827825149</t>
+  </si>
+  <si>
+    <t>1ZRF69236866718473</t>
+  </si>
+  <si>
+    <t>1ZRF69236866731118</t>
+  </si>
+  <si>
+    <t>1ZRF69236865579778</t>
+  </si>
+  <si>
+    <t>1ZRF69236866174015</t>
+  </si>
+  <si>
+    <t>1ZRF69236864469095</t>
+  </si>
+  <si>
+    <t>1ZRF69236865042454</t>
+  </si>
+  <si>
+    <t>1ZRF69236864614267</t>
+  </si>
+  <si>
+    <t>1ZRF69236866086727</t>
+  </si>
+  <si>
+    <t>1ZRF69236865223339</t>
+  </si>
+  <si>
+    <t>1ZRF69236865056501</t>
+  </si>
+  <si>
+    <t>1ZRF69236864846230</t>
+  </si>
+  <si>
+    <t>1ZRF69236864319167</t>
+  </si>
+  <si>
+    <t>1Z93635F6892070541</t>
+  </si>
+  <si>
+    <t>1Z4E30A96898930616</t>
+  </si>
+  <si>
+    <t>1Z032YY49197269821</t>
+  </si>
+  <si>
+    <t>1Z032YY49198797955</t>
+  </si>
+  <si>
+    <t>1Z032YY46887652166</t>
+  </si>
+  <si>
+    <t>1Z032YY49190532423</t>
+  </si>
+  <si>
+    <t>1Z032YY49192837010</t>
+  </si>
+  <si>
+    <t>1Z8FF6136825517880</t>
+  </si>
+  <si>
+    <t>1Z7W4Y036840286969</t>
+  </si>
+  <si>
+    <t>1Z31907X6896240524</t>
+  </si>
+  <si>
+    <t>1Z30V08X6898353325</t>
+  </si>
+  <si>
+    <t>1Z032YY49199237450</t>
+  </si>
+  <si>
+    <t>1Z728RR86814046629</t>
+  </si>
+  <si>
+    <t>1Z728RR80414073059</t>
+  </si>
+  <si>
+    <t>1Z728RR80414066772</t>
+  </si>
+  <si>
+    <t>1Z04VB170428296800</t>
+  </si>
+  <si>
+    <t>1Z728RR80414041904</t>
+  </si>
+  <si>
+    <t>1Z728RR80414043993</t>
+  </si>
+  <si>
+    <t>1Z728RR80414065317</t>
+  </si>
+  <si>
+    <t>1ZV8979K6824909416</t>
+  </si>
+  <si>
+    <t>1ZV8K8976842556214</t>
+  </si>
+  <si>
+    <t>1Z30R0336865371576</t>
+  </si>
+  <si>
+    <t>1Z97W1636811614075</t>
+  </si>
+  <si>
+    <t>1Z9F46200430175982</t>
+  </si>
+  <si>
+    <t>1ZRJ69466826806821</t>
+  </si>
+  <si>
+    <t>1Z57E5476875035525</t>
+  </si>
+  <si>
+    <t>1ZW661006839123836</t>
   </si>
 </sst>
 </file>
@@ -537,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCDA684C-736D-6F4D-BCC3-A305ABCF65B5}">
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C92"/>
   <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19.50390625" customWidth="1"/>
@@ -1059,14 +1176,450 @@
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="1">
-        <v>46227</v>
-      </c>
+      <c r="A50" s="1"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
-        <v>46227</v>
-      </c>
+        <v>46230</v>
+      </c>
+      <c r="B51" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B52" t="s">
+        <v>45</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B54" t="s">
+        <v>47</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B55" t="s">
+        <v>48</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B56" t="s">
+        <v>49</v>
+      </c>
+      <c r="C56" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B57" t="s">
+        <v>50</v>
+      </c>
+      <c r="C57" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B58" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B59" t="s">
+        <v>52</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B60" t="s">
+        <v>53</v>
+      </c>
+      <c r="C60" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B62" t="s">
+        <v>55</v>
+      </c>
+      <c r="C62" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B63" t="s">
+        <v>56</v>
+      </c>
+      <c r="C63" s="1">
+        <v>46250</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B64" t="s">
+        <v>57</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B65" t="s">
+        <v>58</v>
+      </c>
+      <c r="C65" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B66" t="s">
+        <v>59</v>
+      </c>
+      <c r="C66" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B67" t="s">
+        <v>60</v>
+      </c>
+      <c r="C67" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B68" t="s">
+        <v>61</v>
+      </c>
+      <c r="C68" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>46230</v>
+      </c>
+      <c r="B69" t="s">
+        <v>62</v>
+      </c>
+      <c r="C69" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B71" t="s">
+        <v>32</v>
+      </c>
+      <c r="C71" s="1">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B72" t="s">
+        <v>63</v>
+      </c>
+      <c r="C72" s="1">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B73" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46237</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B74" t="s">
+        <v>65</v>
+      </c>
+      <c r="C74" s="1">
+        <v>46238</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B75" t="s">
+        <v>66</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B76" t="s">
+        <v>67</v>
+      </c>
+      <c r="C76" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B77" t="s">
+        <v>68</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B78" t="s">
+        <v>69</v>
+      </c>
+      <c r="C78" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B79" t="s">
+        <v>70</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B80" t="s">
+        <v>71</v>
+      </c>
+      <c r="C80" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B81" t="s">
+        <v>72</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B82" t="s">
+        <v>73</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B83" t="s">
+        <v>74</v>
+      </c>
+      <c r="C83" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B84" t="s">
+        <v>75</v>
+      </c>
+      <c r="C84" s="1">
+        <v>46245</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B85" t="s">
+        <v>76</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46244</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B86" t="s">
+        <v>77</v>
+      </c>
+      <c r="C86" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B87" t="s">
+        <v>78</v>
+      </c>
+      <c r="C87" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B88" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B89" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B90" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" s="1">
+        <v>46251</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>46262</v>
+      </c>
+      <c r="B91" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91" s="1">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
